--- a/datasets/finishing/inventory-brightway.xlsx
+++ b/datasets/finishing/inventory-brightway.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vincentcarrieres/carbonfact/lca/lca/notebooks/science/Carbonfact database/Finishing/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vincentcarrieres/carbonfact/textile-lca-database/datasets/finishing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D7BA7D4-D429-8E40-90D9-D594E95371C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A234C5-0806-9348-8C45-A8E1EF795288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4480" yWindow="-21000" windowWidth="38340" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-5020" yWindow="-21000" windowWidth="38340" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="101">
   <si>
     <t>Database</t>
   </si>
@@ -314,12 +314,6 @@
   </si>
   <si>
     <t>desized polyester fabric, continuous</t>
-  </si>
-  <si>
-    <t>Fabric finishing, Heat-setting, Polyester, Stenter</t>
-  </si>
-  <si>
-    <t>heat-set polyester fabric, stenter</t>
   </si>
   <si>
     <t>Heat, for textile processes, production mix</t>
@@ -668,7 +662,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I307"/>
+  <dimension ref="A1:I291"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="64.1640625" bestFit="1" customWidth="1"/>
@@ -690,7 +684,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -711,7 +705,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -766,13 +760,13 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
         <v>100</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11" t="s">
-        <v>102</v>
       </c>
       <c r="D11" t="s">
         <v>7</v>
@@ -983,13 +977,13 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B26">
         <v>3.5</v>
       </c>
       <c r="C26" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D26" t="s">
         <v>7</v>
@@ -1246,13 +1240,13 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B43">
         <v>1.5</v>
       </c>
       <c r="C43" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D43" t="s">
         <v>7</v>
@@ -1509,13 +1503,13 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B60">
         <v>4.2</v>
       </c>
       <c r="C60" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D60" t="s">
         <v>7</v>
@@ -1657,13 +1651,13 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B72">
         <v>3.5</v>
       </c>
       <c r="C72" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D72" t="s">
         <v>7</v>
@@ -1805,13 +1799,13 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B84">
         <v>2</v>
       </c>
       <c r="C84" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D84" t="s">
         <v>7</v>
@@ -2022,13 +2016,13 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B99">
         <v>10.3</v>
       </c>
       <c r="C99" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D99" t="s">
         <v>7</v>
@@ -2331,13 +2325,13 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B118">
         <v>2</v>
       </c>
       <c r="C118" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D118" t="s">
         <v>7</v>
@@ -2571,13 +2565,13 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B134">
         <v>3.5</v>
       </c>
       <c r="C134" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D134" t="s">
         <v>7</v>
@@ -2834,13 +2828,13 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B151">
         <v>3.5</v>
       </c>
       <c r="C151" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D151" t="s">
         <v>7</v>
@@ -3074,13 +3068,13 @@
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B167">
         <v>4</v>
       </c>
       <c r="C167" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D167" t="s">
         <v>7</v>
@@ -3587,13 +3581,13 @@
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B206">
         <v>4.2</v>
       </c>
       <c r="C206" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D206" t="s">
         <v>7</v>
@@ -3850,13 +3844,13 @@
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B223">
         <v>3.5</v>
       </c>
       <c r="C223" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D223" t="s">
         <v>7</v>
@@ -4090,13 +4084,13 @@
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B239">
         <v>7.54</v>
       </c>
       <c r="C239" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D239" t="s">
         <v>7</v>
@@ -4238,13 +4232,13 @@
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B251">
         <v>6.37</v>
       </c>
       <c r="C251" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D251" t="s">
         <v>7</v>
@@ -4386,13 +4380,13 @@
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B263">
         <v>2</v>
       </c>
       <c r="C263" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D263" t="s">
         <v>7</v>
@@ -4534,13 +4528,13 @@
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B275">
         <v>6.91</v>
       </c>
       <c r="C275" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D275" t="s">
         <v>7</v>
@@ -4682,13 +4676,13 @@
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B287">
         <v>9</v>
       </c>
       <c r="C287" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D287" t="s">
         <v>7</v>
@@ -4726,7 +4720,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>35</v>
       </c>
@@ -4749,7 +4743,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>37</v>
       </c>
@@ -4772,7 +4766,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>40</v>
       </c>
@@ -4792,246 +4786,6 @@
         <v>42</v>
       </c>
       <c r="H291" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A293" t="s">
-        <v>2</v>
-      </c>
-      <c r="B293" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A294" t="s">
-        <v>3</v>
-      </c>
-      <c r="B294">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A295" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A296" t="s">
-        <v>5</v>
-      </c>
-      <c r="B296" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A297" t="s">
-        <v>6</v>
-      </c>
-      <c r="B297" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A298" t="s">
-        <v>8</v>
-      </c>
-      <c r="B298" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A299" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A300" t="s">
-        <v>11</v>
-      </c>
-      <c r="B300" t="s">
-        <v>12</v>
-      </c>
-      <c r="C300" t="s">
-        <v>5</v>
-      </c>
-      <c r="D300" t="s">
-        <v>6</v>
-      </c>
-      <c r="E300" t="s">
-        <v>8</v>
-      </c>
-      <c r="F300" t="s">
-        <v>13</v>
-      </c>
-      <c r="G300" t="s">
-        <v>14</v>
-      </c>
-      <c r="H300" t="s">
-        <v>15</v>
-      </c>
-      <c r="I300" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A301" t="s">
-        <v>98</v>
-      </c>
-      <c r="B301">
-        <v>1</v>
-      </c>
-      <c r="C301" t="s">
-        <v>99</v>
-      </c>
-      <c r="D301" t="s">
-        <v>7</v>
-      </c>
-      <c r="E301" t="s">
-        <v>27</v>
-      </c>
-      <c r="G301" t="s">
-        <v>16</v>
-      </c>
-      <c r="H301" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A302" t="s">
-        <v>28</v>
-      </c>
-      <c r="B302">
-        <v>9.7000000000000003E-2</v>
-      </c>
-      <c r="C302" t="s">
-        <v>29</v>
-      </c>
-      <c r="D302" t="s">
-        <v>7</v>
-      </c>
-      <c r="E302" t="s">
-        <v>30</v>
-      </c>
-      <c r="G302" t="s">
-        <v>20</v>
-      </c>
-      <c r="H302" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A303" t="s">
-        <v>100</v>
-      </c>
-      <c r="B303">
-        <v>8.75</v>
-      </c>
-      <c r="C303" t="s">
-        <v>102</v>
-      </c>
-      <c r="D303" t="s">
-        <v>7</v>
-      </c>
-      <c r="E303" t="s">
-        <v>9</v>
-      </c>
-      <c r="G303" t="s">
-        <v>20</v>
-      </c>
-      <c r="H303" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A304" t="s">
-        <v>31</v>
-      </c>
-      <c r="B304">
-        <v>4.1000000000000002E-2</v>
-      </c>
-      <c r="C304" t="s">
-        <v>32</v>
-      </c>
-      <c r="D304" t="s">
-        <v>19</v>
-      </c>
-      <c r="E304" t="s">
-        <v>27</v>
-      </c>
-      <c r="G304" t="s">
-        <v>20</v>
-      </c>
-      <c r="H304" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A305" t="s">
-        <v>35</v>
-      </c>
-      <c r="B305">
-        <v>2.5</v>
-      </c>
-      <c r="C305" t="s">
-        <v>36</v>
-      </c>
-      <c r="D305" t="s">
-        <v>7</v>
-      </c>
-      <c r="E305" t="s">
-        <v>27</v>
-      </c>
-      <c r="G305" t="s">
-        <v>20</v>
-      </c>
-      <c r="H305" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A306" t="s">
-        <v>37</v>
-      </c>
-      <c r="B306">
-        <v>-2.2499999999999998E-3</v>
-      </c>
-      <c r="C306" t="s">
-        <v>38</v>
-      </c>
-      <c r="D306" t="s">
-        <v>19</v>
-      </c>
-      <c r="E306" t="s">
-        <v>39</v>
-      </c>
-      <c r="G306" t="s">
-        <v>20</v>
-      </c>
-      <c r="H306" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A307" t="s">
-        <v>40</v>
-      </c>
-      <c r="B307">
-        <v>2.5000000000000001E-4</v>
-      </c>
-      <c r="D307" t="s">
-        <v>7</v>
-      </c>
-      <c r="E307" t="s">
-        <v>39</v>
-      </c>
-      <c r="F307" t="s">
-        <v>41</v>
-      </c>
-      <c r="G307" t="s">
-        <v>42</v>
-      </c>
-      <c r="H307" t="s">
         <v>43</v>
       </c>
     </row>
